--- a/Task_04/DucNVFX14814_Data_Design_Review_Checklist.xlsx
+++ b/Task_04/DucNVFX14814_Data_Design_Review_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Funix\4. CC4\5. LAB301x\LAB301x_01\Task_04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D053AAD-251F-45C3-9EF7-513311BEBD5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE143A0-6AFE-46A2-8C1B-180D5293EEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>CHECKLIST TỰ KIỂM TRA - TASK 4: THIẾT KẾ CSDL VÀ NHẬP DỮ LIỆU MẪU</t>
   </si>
@@ -67,12 +67,6 @@
     <t>Đã chèn ảnh chụp EER Diagram từ MySQL Workbench vào file Data_Design.docx</t>
   </si>
   <si>
-    <t>4 bảng: users, lottery_tickets, lottery_prizes, lottery_history</t>
-  </si>
-  <si>
-    <t>PK: id (AUTO_INCREMENT) mỗi bảng; FK: lottery_tickets.company_id/created_by, lottery_prizes.ticket_id, draw_history.user_id/ticket_id</t>
-  </si>
-  <si>
     <t>File DucNVFX14814_DB.sql</t>
   </si>
   <si>
@@ -83,6 +77,15 @@
   </si>
   <si>
     <t>MySQL Server 8.0 đã cài và chạy dưới dạng Windows Service (MySQL80)</t>
+  </si>
+  <si>
+    <t>7 bảng: users, lottery_regions, lottery_companys, lottery_prize_configs, lottery_tickets, lottery_ticket_items, lottery_history</t>
+  </si>
+  <si>
+    <t>Đã đầy đủ, ngoại trừ bảng lottery_regions do giới hạn của data</t>
+  </si>
+  <si>
+    <t>Đầy đủ các khóa chính và khóa ngoại</t>
   </si>
 </sst>
 </file>
@@ -176,14 +179,7 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -192,6 +188,13 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -498,151 +501,153 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6" style="3" customWidth="1"/>
-    <col min="2" max="2" width="55" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16" style="3" customWidth="1"/>
-    <col min="4" max="4" width="55" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="8.796875" style="3"/>
+    <col min="1" max="1" width="6" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="4" width="68.09765625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>3</v>
-      </c>
-      <c r="B7" s="7" t="s">
+    <row r="10" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
         <v>8</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>4</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="7"/>
-    </row>
-    <row r="9" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <v>5</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <v>6</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="B12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
-        <v>7</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
-        <v>8</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
